--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -1,83 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rithika\Downloads\leave-agent\leaveagent\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C154E9-D95C-4825-9D8E-A2A5CD1796C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="LeaveRequests" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t>employee</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>approved_by</t>
-  </si>
-  <si>
-    <t>requested_at</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>devtools</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>WFH</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>full_day</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>2026-03-10T10:43:49.972Z</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -446,78 +396,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="8" max="8" width="18.58203125" customWidth="1"/>
-    <col min="9" max="9" width="24.25" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J1"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>employee</v>
+      </c>
+      <c r="B1" t="str">
+        <v>email</v>
+      </c>
+      <c r="C1" t="str">
+        <v>type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>end_date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>duration</v>
+      </c>
+      <c r="G1" t="str">
+        <v>status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>approved_by</v>
+      </c>
+      <c r="I1" t="str">
+        <v>requested_at</v>
+      </c>
+      <c r="J1" t="str">
+        <v>updated_at</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,9 +431,243 @@
         <v>updated_at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B2" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C2" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-03-11T08:19:37.794Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B3" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-03-11T09:20:09.264Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B4" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-03-11T10:24:15.762Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B5" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-03-11T10:26:49.345Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B6" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-03-11T10:34:33.535Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B7" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-03-11T10:37:35.904Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B8" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-03-11T11:00:37.172Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B9" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-03-11T11:04:10.056Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B10" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-03-11T11:17:20.470Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,15 +419,21 @@
         <v>duration</v>
       </c>
       <c r="G1" t="str">
+        <v>days_count</v>
+      </c>
+      <c r="H1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="I1" t="str">
         <v>status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>approved_by</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>requested_at</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>updated_at</v>
       </c>
     </row>
@@ -439,235 +445,33 @@
         <v>devtools@company.com</v>
       </c>
       <c r="C2" t="str">
-        <v>WFH</v>
+        <v>PATERNITY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="F2" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2" t="str">
         <v/>
       </c>
-      <c r="F2" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Pending</v>
       </c>
-      <c r="I2" t="str">
-        <v>2026-03-11T08:19:37.794Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B3" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C3" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-03-11T09:20:09.264Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B4" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C4" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-03-11T10:24:15.762Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B5" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C5" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-03-11T10:26:49.345Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B6" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2026-03-11T10:34:33.535Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B7" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C7" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I7" t="str">
-        <v>2026-03-11T10:37:35.904Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B8" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C8" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I8" t="str">
-        <v>2026-03-11T11:00:37.172Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B9" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C9" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I9" t="str">
-        <v>2026-03-11T11:04:10.056Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>devtools</v>
-      </c>
-      <c r="B10" t="str">
-        <v>devtools@company.com</v>
-      </c>
-      <c r="C10" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="I10" t="str">
-        <v>2026-03-11T11:17:20.470Z</v>
+      <c r="K2" t="str">
+        <v>2026-03-12T07:05:44.314Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="LeaveRequests" sheetId="1" r:id="rId1"/>
+    <sheet name="MonthlySummary" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,9 +470,265 @@
         <v>2026-03-12T07:05:44.314Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B3" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-03-13T07:38:07.811Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B4" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-03-13T07:40:04.673Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B5" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="F5" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-03-13T07:40:18.905Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B6" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v>PATERNITY</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-08-14</v>
+      </c>
+      <c r="F6" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2026-03-13T07:47:31.948Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B7" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>PATERNITY</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="F7" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-03-13T07:50:53.338Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B8" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PATERNITY</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="F8" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-03-13T08:01:00.396Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>devtools</v>
+      </c>
+      <c r="B9" t="str">
+        <v>devtools@company.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PATERNITY</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="F9" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-03-13T08:01:30.796Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Month</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Emp</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Leaves</v>
+      </c>
+      <c r="D1" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="E1" t="str">
+        <v>unapproved</v>
+      </c>
+      <c r="F1" t="str">
+        <v>approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,25 +440,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>devtools</v>
+        <v>Rithika MR</v>
       </c>
       <c r="B2" t="str">
-        <v>devtools@company.com</v>
+        <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C2" t="str">
-        <v>PATERNITY</v>
+        <v>WFH</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>multi_day</v>
+        <v>full_day</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -467,15 +467,15 @@
         <v>Pending</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-03-12T07:05:44.314Z</v>
+        <v>2026-03-13T10:59:54.868Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>devtools</v>
+        <v>Varsha M</v>
       </c>
       <c r="B3" t="str">
-        <v>devtools@company.com</v>
+        <v>varsha.m@8thelement.ai</v>
       </c>
       <c r="C3" t="str">
         <v>WFH</v>
@@ -496,24 +496,30 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Rithika MR</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-03-13T07:38:07.811Z</v>
+        <v>2026-03-13T11:04:37.945Z</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-03-13T11:08:09.299Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>devtools</v>
+        <v>Varsha M</v>
       </c>
       <c r="B4" t="str">
-        <v>devtools@company.com</v>
+        <v>varsha.m@8thelement.ai</v>
       </c>
       <c r="C4" t="str">
-        <v>LEAVE</v>
+        <v>WFH</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-10</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -528,33 +534,39 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Varsha M</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-03-13T07:40:04.673Z</v>
+        <v>2026-03-13T11:12:49.043Z</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-03-13T11:13:07.062Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>devtools</v>
+        <v>Varsha M</v>
       </c>
       <c r="B5" t="str">
-        <v>devtools@company.com</v>
+        <v>varsha.m@8thelement.ai</v>
       </c>
       <c r="C5" t="str">
-        <v>LEAVE</v>
+        <v>WFH</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-03</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>multi_day</v>
+        <v>full_day</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -563,147 +575,399 @@
         <v>Pending</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-03-13T07:40:18.905Z</v>
+        <v>2026-03-13T11:17:39.721Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>devtools</v>
+        <v>Rithika MR</v>
       </c>
       <c r="B6" t="str">
-        <v>devtools@company.com</v>
+        <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C6" t="str">
-        <v>PATERNITY</v>
+        <v>WFH</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-08-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-14</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>multi_day</v>
+        <v>full_day</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Varsha M</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-03-13T07:47:31.948Z</v>
+        <v>2026-03-13T11:18:10.664Z</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-03-13T11:18:42.047Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>devtools</v>
+        <v>Varsha M</v>
       </c>
       <c r="B7" t="str">
-        <v>devtools@company.com</v>
+        <v>varsha.m@8thelement.ai</v>
       </c>
       <c r="C7" t="str">
-        <v>PATERNITY</v>
+        <v>WFH</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-07</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>multi_day</v>
+        <v>full_day</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Rithika MR</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-03-13T07:50:53.338Z</v>
+        <v>2026-03-13T11:19:18.625Z</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-03-13T11:19:24.088Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>devtools</v>
+        <v>Rithika MR</v>
       </c>
       <c r="B8" t="str">
-        <v>devtools@company.com</v>
+        <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C8" t="str">
-        <v>PATERNITY</v>
+        <v>WFH</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-23</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-03-27</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>multi_day</v>
+        <v>full_day</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Varsha M</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-03-13T08:01:00.396Z</v>
+        <v>2026-03-13T11:20:01.427Z</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-03-13T11:20:06.445Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>devtools</v>
+        <v>Rithika MR</v>
       </c>
       <c r="B9" t="str">
-        <v>devtools@company.com</v>
+        <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C9" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Rejected</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-03-13T11:20:35.542Z</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-03-13T11:20:40.400Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B10" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SICK</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-03-13T11:21:49.772Z</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-03-13T11:22:03.448Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="B11" t="str">
+        <v>varsha.m@8thelement.ai</v>
+      </c>
+      <c r="C11" t="str">
         <v>PATERNITY</v>
       </c>
-      <c r="D9" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="F9" t="str">
+      <c r="D11" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="F11" t="str">
         <v>multi_day</v>
       </c>
-      <c r="G9">
+      <c r="G11">
         <v>5</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="K9" t="str">
-        <v>2026-03-13T08:01:30.796Z</v>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Rejected</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-03-13T11:22:53.286Z</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-03-13T11:24:39.742Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="B12" t="str">
+        <v>varsha.m@8thelement.ai</v>
+      </c>
+      <c r="C12" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-03-13T11:26:14.426Z</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-03-13T11:26:23.053Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B13" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C13" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-03-13T11:30:13.859Z</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-03-13T11:30:21.431Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B14" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C14" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Rejected</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-03-13T11:31:32.661Z</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-03-13T11:31:39.104Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B15" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C15" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Rejected</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Tushar Thapliyal</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-03-15T07:10:04.459Z</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-03-15T07:10:30.264Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -725,10 +989,69 @@
         <v>approved</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>03/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>03/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>04/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,10 +446,10 @@
         <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C2" t="str">
-        <v>WFH</v>
+        <v>LEAVE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -467,21 +467,21 @@
         <v>Pending</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-03-13T10:59:54.868Z</v>
+        <v>2026-03-15T07:40:06.526Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Varsha M</v>
+        <v>Rithika MR</v>
       </c>
       <c r="B3" t="str">
-        <v>varsha.m@8thelement.ai</v>
+        <v>rithika.mr@8thelement.ai</v>
       </c>
       <c r="C3" t="str">
-        <v>WFH</v>
+        <v>LEAVE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -502,465 +502,15 @@
         <v>Rithika MR</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-03-13T11:04:37.945Z</v>
+        <v>2026-03-15T07:56:36.966Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-03-13T11:08:09.299Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="B4" t="str">
-        <v>varsha.m@8thelement.ai</v>
-      </c>
-      <c r="C4" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2026-03-13T11:12:49.043Z</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-03-13T11:13:07.062Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="B5" t="str">
-        <v>varsha.m@8thelement.ai</v>
-      </c>
-      <c r="C5" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="K5" t="str">
-        <v>2026-03-13T11:17:39.721Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B6" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C6" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K6" t="str">
-        <v>2026-03-13T11:18:10.664Z</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-03-13T11:18:42.047Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="B7" t="str">
-        <v>varsha.m@8thelement.ai</v>
-      </c>
-      <c r="C7" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2026-03-13T11:19:18.625Z</v>
-      </c>
-      <c r="L7" t="str">
-        <v>2026-03-13T11:19:24.088Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B8" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C8" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2026-03-13T11:20:01.427Z</v>
-      </c>
-      <c r="L8" t="str">
-        <v>2026-03-13T11:20:06.445Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B9" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C9" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-08</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>Rejected</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K9" t="str">
-        <v>2026-03-13T11:20:35.542Z</v>
-      </c>
-      <c r="L9" t="str">
-        <v>2026-03-13T11:20:40.400Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B10" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C10" t="str">
-        <v>SICK</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2026-03-13T11:21:49.772Z</v>
-      </c>
-      <c r="L10" t="str">
-        <v>2026-03-13T11:22:03.448Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="B11" t="str">
-        <v>varsha.m@8thelement.ai</v>
-      </c>
-      <c r="C11" t="str">
-        <v>PATERNITY</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="F11" t="str">
-        <v>multi_day</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>Rejected</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="K11" t="str">
-        <v>2026-03-13T11:22:53.286Z</v>
-      </c>
-      <c r="L11" t="str">
-        <v>2026-03-13T11:24:39.742Z</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="B12" t="str">
-        <v>varsha.m@8thelement.ai</v>
-      </c>
-      <c r="C12" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="K12" t="str">
-        <v>2026-03-13T11:26:14.426Z</v>
-      </c>
-      <c r="L12" t="str">
-        <v>2026-03-13T11:26:23.053Z</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B13" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C13" t="str">
-        <v>LEAVE</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K13" t="str">
-        <v>2026-03-13T11:30:13.859Z</v>
-      </c>
-      <c r="L13" t="str">
-        <v>2026-03-13T11:30:21.431Z</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B14" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C14" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>Rejected</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Varsha M</v>
-      </c>
-      <c r="K14" t="str">
-        <v>2026-03-13T11:31:32.661Z</v>
-      </c>
-      <c r="L14" t="str">
-        <v>2026-03-13T11:31:39.104Z</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Rithika MR</v>
-      </c>
-      <c r="B15" t="str">
-        <v>rithika.mr@8thelement.ai</v>
-      </c>
-      <c r="C15" t="str">
-        <v>WFH</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v>full_day</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>Rejected</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Tushar Thapliyal</v>
-      </c>
-      <c r="K15" t="str">
-        <v>2026-03-15T07:10:04.459Z</v>
-      </c>
-      <c r="L15" t="str">
-        <v>2026-03-15T07:10:30.264Z</v>
+        <v>2026-03-15T07:58:43.814Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -997,7 +547,7 @@
         <v>Varsha M</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -1006,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +567,7 @@
         <v>Rithika MR</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1026,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">

--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,7 +449,7 @@
         <v>LEAVE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -464,10 +464,16 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>Pending</v>
+        <v>Approved</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Varsha M</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-03-15T07:40:06.526Z</v>
+        <v>2026-03-16T06:42:57.310Z</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-03-16T06:43:04.162Z</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +487,7 @@
         <v>LEAVE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-30</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -499,18 +505,94 @@
         <v>Approved</v>
       </c>
       <c r="J3" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-03-16T06:43:32.228Z</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-03-16T06:43:35.647Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
         <v>Rithika MR</v>
       </c>
-      <c r="K3" t="str">
-        <v>2026-03-15T07:56:36.966Z</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-03-15T07:58:43.814Z</v>
+      <c r="B4" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SICK</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Rejected</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-03-16T06:43:58.663Z</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-03-16T06:44:02.456Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B5" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C5" t="str">
+        <v>WFH</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-03-16T06:44:18.472Z</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-03-16T06:44:25.178Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -547,16 +629,16 @@
         <v>Varsha M</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -567,16 +649,16 @@
         <v>Rithika MR</v>
       </c>
       <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +669,7 @@
         <v>Rithika MR</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -596,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/leaveagent/data/LeaveRequests.xlsx
+++ b/leaveagent/data/LeaveRequests.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,9 +590,199 @@
         <v>2026-03-16T06:44:25.178Z</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B6" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C6" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>exam</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2026-03-16T07:24:17.846Z</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-03-16T07:34:53.790Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B7" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C7" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-03-16T07:44:42.399Z</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-03-16T07:45:36.228Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="B8" t="str">
+        <v>rithika.mr@8thelement.ai</v>
+      </c>
+      <c r="C8" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-03-16T08:01:00.103Z</v>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-03-16T08:01:06.251Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="B9" t="str">
+        <v>varsha.m@8thelement.ai</v>
+      </c>
+      <c r="C9" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>full_day</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-03-16T08:04:24.020Z</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-03-16T08:08:58.159Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Varsha M</v>
+      </c>
+      <c r="B10" t="str">
+        <v>varsha.m@8thelement.ai</v>
+      </c>
+      <c r="C10" t="str">
+        <v>LEAVE</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="F10" t="str">
+        <v>multi_day</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Rithika MR</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-03-16T08:07:54.113Z</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-03-16T08:09:02.491Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -629,7 +819,7 @@
         <v>Varsha M</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -638,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -649,7 +839,7 @@
         <v>Rithika MR</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -658,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
